--- a/dynamics/src/dynamics/xlsx/dynamics_space_calc_axis1_positive.xlsx
+++ b/dynamics/src/dynamics/xlsx/dynamics_space_calc_axis1_positive.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,325 +447,55 @@
           <t>axis 6</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>torque 1</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>torque 2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>torque 3</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>torque 4</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>torque 5</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>torque 6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-3.105846359614336</v>
+        <v>3.270518011799142e-16</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.797717673423648</v>
+        <v>-3.724497729328131</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.879169797576249</v>
+        <v>0.2733045811622971</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.719117641594874</v>
+        <v>-0.1183336325425818</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.472294534510556</v>
+        <v>0.0003108179666699722</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.934520051613317</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>-2.954886845896354</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-1.820614101644493</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-2.982178426418986</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-2.441030711407651</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-2.394875499313345</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-1.73460039845043</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>-2.617474039155551</v>
-      </c>
-      <c r="B4" t="n">
-        <v>-1.377093236573725</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.141592651662259</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-2.503868694562557</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-2.169678412223743</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-1.399817367683279</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>-2.458665728285796</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.102323639962608</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-3.038919469941506</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.258930416409568</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-2.048907499719317</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-1.279584662781652</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>-2.309433650369634</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.5787655390764247</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-2.940360138225099</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.724615859304005</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.930664450498764</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-1.179821307151273</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>-2.189516263826585</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.6953205589482614</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-2.860677806731916</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.550998559810551</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.833416652756525</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1.106075894443337</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>-2.094455775171391</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6930700915574537</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-2.796651515967203</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.501583633678966</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-1.755380765032476</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-1.050387947768271</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>-2.022162341884876</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.6363366598374385</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-2.748141522365028</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.516165518118304</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-1.695657670845798</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1.009151917204456</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>-1.972168172866962</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.5492668157498214</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-2.715410745978167</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.57343065715726</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-1.654229258781072</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.9810133854518972</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>-1.945771797195917</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.4420616750925339</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-2.698536668405741</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.664831579265055</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1.632327080100651</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.9662412335137427</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>-1.946566673473681</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.3178998640961139</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-2.697168296328906</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.787597558341597</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-1.632986841386029</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.9666854152255109</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>-1.981375272239499</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.1743389007558205</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-2.710392844782884</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.942890626687676</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.661864744885345</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.9861779472731842</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>-2.061864424715696</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.001302389465449945</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-2.736559539681618</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.136442010356113</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.72848865110369</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1.031702131072497</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>-2.208001791641406</v>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.2272491969083704</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-2.772509222216418</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.382442517682342</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-1.848506365539506</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.117155718388279</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>-2.46429497755891</v>
-      </c>
-      <c r="B16" t="n">
-        <v>-0.5880763900645657</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-2.808462212572391</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.71703227947902</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-2.053289657924943</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-1.283568894377026</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>-2.875782976383486</v>
-      </c>
-      <c r="B17" t="n">
-        <v>-1.176876806618164</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-2.799046750262529</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.080569817559828</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-2.34757520371836</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-1.643680589132697</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
